--- a/exports/TORNTPHARM_full_report.xlsx
+++ b/exports/TORNTPHARM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.89</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44586.55208333334</v>
+        <v>44588.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1568.75</v>
+        <v>1355.3</v>
       </c>
       <c r="I2" t="n">
         <v>1537.604447615003</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08</v>
+        <v>-13.54</v>
       </c>
       <c r="L2" t="n">
-        <v>2.01</v>
+        <v>15.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>6.29</v>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>14.36</v>
       </c>
       <c r="O2" t="n">
         <v>0.73</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.46</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44614.55208333334</v>
+        <v>44615.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1349</v>
+        <v>1370.9</v>
       </c>
       <c r="I3" t="n">
         <v>1358.36236034186</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>-1.15</v>
       </c>
       <c r="L3" t="n">
         <v>8.460000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1369.5</v>
+        <v>1356.5</v>
       </c>
       <c r="I4" t="n">
         <v>1366.78979427108</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1</v>
+        <v>-1.05</v>
       </c>
       <c r="L4" t="n">
         <v>4.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.71</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44669.55208333334</v>
+        <v>44670.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1425.5</v>
+        <v>1436.75</v>
       </c>
       <c r="I5" t="n">
         <v>1431.11975244264</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.09</v>
+        <v>-5.92</v>
       </c>
       <c r="L5" t="n">
-        <v>6.52</v>
+        <v>7.04</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>4.84</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1374.5</v>
+        <v>1361.95</v>
       </c>
       <c r="I6" t="n">
         <v>1367.248640900887</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.33</v>
+        <v>-5.21</v>
       </c>
       <c r="L6" t="n">
-        <v>5.53</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26</v>
+        <v>1.42</v>
       </c>
       <c r="N6" t="n">
         <v>2.77</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44701.38541666666</v>
+        <v>44701.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1317.5</v>
+        <v>1337.5</v>
       </c>
       <c r="I7" t="n">
         <v>1326.411093706882</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3.26</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
         <v>4.16</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.94</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1500</v>
+        <v>1479.2</v>
       </c>
       <c r="I8" t="n">
         <v>1491.400358085857</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>118</v>
+        <v>118.8333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>12.15</v>
+        <v>10.59</v>
       </c>
       <c r="L8" t="n">
         <v>4.58</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1500</v>
+        <v>1543.8</v>
       </c>
       <c r="I9" t="n">
         <v>1540.298475425228</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.41</v>
+        <v>-4.37</v>
       </c>
       <c r="L9" t="n">
         <v>5.61</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44888.55208333334</v>
+        <v>44889.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1629.1</v>
+        <v>1615.35</v>
       </c>
       <c r="I10" t="n">
         <v>1615.602588065343</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
-        <v>5.53</v>
+        <v>4.63</v>
       </c>
       <c r="L10" t="n">
         <v>6.15</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44943.55208333334</v>
+        <v>44944.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1588</v>
+        <v>1609.8</v>
       </c>
       <c r="I11" t="n">
         <v>1591.222072347123</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K11" t="n">
-        <v>1.69</v>
+        <v>0.34</v>
       </c>
       <c r="L11" t="n">
         <v>3.38</v>
@@ -1068,7 +1199,7 @@
         <v>1.37</v>
       </c>
       <c r="N11" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
         <v>-1.23</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44951.38541666666</v>
+        <v>44951.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1565.05</v>
+        <v>1553</v>
       </c>
       <c r="I12" t="n">
         <v>1560.142676164969</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.78</v>
+        <v>-3.53</v>
       </c>
       <c r="L12" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="M12" t="n">
         <v>0.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44999.38541666666</v>
+        <v>44999.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1513.55</v>
+        <v>1525</v>
       </c>
       <c r="I13" t="n">
         <v>1520.888029499764</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K13" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.22</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.26</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1981</v>
+        <v>1944.35</v>
       </c>
       <c r="I14" t="n">
         <v>1965.481254497396</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>161</v>
+        <v>161.8333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>29.9</v>
+        <v>27.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>217</v>
+        <v>218</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.15</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1868</v>
+        <v>1924.55</v>
       </c>
       <c r="I15" t="n">
         <v>1891.744936934976</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>3.93</v>
+        <v>1.02</v>
       </c>
       <c r="L15" t="n">
         <v>3.33</v>
@@ -1296,7 +1475,7 @@
         <v>1.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
         <v>-2.22</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45204.38541666666</v>
+        <v>45204.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1856.25</v>
+        <v>1852.15</v>
       </c>
       <c r="I16" t="n">
         <v>1853.630725254129</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.55</v>
+        <v>-3.76</v>
       </c>
       <c r="L16" t="n">
         <v>5.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>4.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1875.8</v>
+        <v>1934.45</v>
       </c>
       <c r="I17" t="n">
         <v>1930.835930715221</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.28</v>
+        <v>-4.44</v>
       </c>
       <c r="L17" t="n">
-        <v>4.74</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O17" t="n">
         <v>-0.47</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45267.55208333334</v>
+        <v>45268.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2100</v>
+        <v>2051.5</v>
       </c>
       <c r="I18" t="n">
         <v>2058.480426834426</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K18" t="n">
-        <v>8.56</v>
+        <v>6.05</v>
       </c>
       <c r="L18" t="n">
         <v>5.78</v>
@@ -1467,7 +1682,7 @@
         <v>0.51</v>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
         <v>2.3</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.01</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45275.55208333334</v>
+        <v>45278.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2100</v>
+        <v>2138.1</v>
       </c>
       <c r="I19" t="n">
         <v>2136.994432812101</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.36</v>
+        <v>-4.22</v>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
         <v>0.48</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
         <v>-1.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45366.55208333334</v>
+        <v>45369.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2595</v>
+        <v>2562.2</v>
       </c>
       <c r="I20" t="n">
         <v>2584.833553212409</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
-        <v>21.37</v>
+        <v>19.84</v>
       </c>
       <c r="L20" t="n">
         <v>2.01</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.8</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2620</v>
+        <v>2675</v>
       </c>
       <c r="I21" t="n">
         <v>2661.95576400383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.26</v>
+        <v>-4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>4.69</v>
       </c>
       <c r="M21" t="n">
         <v>1.98</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45397.38541666666</v>
+        <v>45397.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>2550.25</v>
+        <v>2516.55</v>
       </c>
       <c r="I22" t="n">
         <v>2531.318235479169</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.66</v>
+        <v>-5.92</v>
       </c>
       <c r="L22" t="n">
-        <v>5.61</v>
+        <v>6.02</v>
       </c>
       <c r="M22" t="n">
         <v>2.26</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.96</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45405.55208333334</v>
+        <v>45406.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2638</v>
+        <v>2686.65</v>
       </c>
       <c r="I23" t="n">
         <v>2653.008123905264</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.83</v>
+        <v>-6.76</v>
       </c>
       <c r="L23" t="n">
-        <v>5.13</v>
+        <v>7.17</v>
       </c>
       <c r="M23" t="n">
         <v>0.85</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.55</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45419.55208333334</v>
+        <v>45420.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2612.25</v>
+        <v>2601</v>
       </c>
       <c r="I24" t="n">
         <v>2603.443996607634</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.77</v>
+        <v>-3.19</v>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="M24" t="n">
         <v>0.07000000000000001</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2652.35</v>
+        <v>2685.3</v>
       </c>
       <c r="I25" t="n">
         <v>2682.763655957312</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.97</v>
+        <v>-3.24</v>
       </c>
       <c r="L25" t="n">
-        <v>2.08</v>
+        <v>3.73</v>
       </c>
       <c r="M25" t="n">
         <v>0.42</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.42</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3355</v>
+        <v>3328</v>
       </c>
       <c r="I26" t="n">
         <v>3350.882729209675</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>125.1666666666667</v>
+        <v>126</v>
       </c>
       <c r="K26" t="n">
-        <v>24.94</v>
+        <v>23.93</v>
       </c>
       <c r="L26" t="n">
         <v>4.28</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.64</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45573.38541666666</v>
+        <v>45573.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>3450.35</v>
+        <v>3537</v>
       </c>
       <c r="I27" t="n">
         <v>3490.927271337449</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.68</v>
+        <v>-6.28</v>
       </c>
       <c r="L27" t="n">
-        <v>5.78</v>
+        <v>6.31</v>
       </c>
       <c r="M27" t="n">
         <v>0.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.18</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45587.38541666666</v>
+        <v>45587.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>3358.75</v>
+        <v>3329.85</v>
       </c>
       <c r="I28" t="n">
         <v>3345.967599197169</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.04</v>
+        <v>-5.86</v>
       </c>
       <c r="L28" t="n">
-        <v>5.34</v>
+        <v>5.89</v>
       </c>
       <c r="M28" t="n">
         <v>0.48</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.55</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45621.38541666666</v>
+        <v>45621.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>3225</v>
+        <v>3272.5</v>
       </c>
       <c r="I29" t="n">
         <v>3239.796278451216</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="L29" t="n">
         <v>5.46</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.46</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3399</v>
+        <v>3336.8</v>
       </c>
       <c r="I30" t="n">
         <v>3347.003098530343</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>3.87</v>
+        <v>1.96</v>
       </c>
       <c r="L30" t="n">
         <v>3.18</v>
@@ -2151,7 +2510,7 @@
         <v>1.26</v>
       </c>
       <c r="N30" t="n">
-        <v>1.54</v>
+        <v>2.27</v>
       </c>
       <c r="O30" t="n">
         <v>3.2</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3248.9</v>
+        <v>3340.9</v>
       </c>
       <c r="I31" t="n">
         <v>3298.581217576104</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>2.63</v>
+        <v>-0.12</v>
       </c>
       <c r="L31" t="n">
         <v>2.4</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>6.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3205</v>
+        <v>3167.05</v>
       </c>
       <c r="I32" t="n">
         <v>3178.393089929482</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.07</v>
+        <v>-5.2</v>
       </c>
       <c r="L32" t="n">
-        <v>4.63</v>
+        <v>6.58</v>
       </c>
       <c r="M32" t="n">
-        <v>0.42</v>
+        <v>2.62</v>
       </c>
       <c r="N32" t="n">
         <v>2.42</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.14</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45728.38541666666</v>
+        <v>45728.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>3079.85</v>
+        <v>3101.55</v>
       </c>
       <c r="I33" t="n">
         <v>3092.798872876686</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="L33" t="n">
         <v>5.22</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.43</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3170.7</v>
+        <v>3134.2</v>
       </c>
       <c r="I34" t="n">
         <v>3169.331165364269</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>2.23</v>
+        <v>1.05</v>
       </c>
       <c r="L34" t="n">
         <v>2.04</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.58</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>3243.8</v>
+        <v>3260</v>
       </c>
       <c r="I35" t="n">
         <v>3252.92051936368</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.5</v>
+        <v>-4.01</v>
       </c>
       <c r="L35" t="n">
         <v>7.58</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>3.45</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45873.38541666666</v>
+        <v>45873.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>3617.6</v>
+        <v>3604.7</v>
       </c>
       <c r="I36" t="n">
         <v>3609.278115379295</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>52.83333333333334</v>
+        <v>53</v>
       </c>
       <c r="K36" t="n">
-        <v>10.97</v>
+        <v>10.57</v>
       </c>
       <c r="L36" t="n">
         <v>3.68</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.67</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3650.8</v>
+        <v>3670</v>
       </c>
       <c r="I37" t="n">
         <v>3660.781020440797</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.28</v>
+        <v>-1.81</v>
       </c>
       <c r="L37" t="n">
         <v>2.64</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>3.37</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>3572.5</v>
+        <v>3542.9</v>
       </c>
       <c r="I38" t="n">
         <v>3546.421806399258</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.66</v>
+        <v>-3.46</v>
       </c>
       <c r="L38" t="n">
-        <v>2.84</v>
+        <v>4.01</v>
       </c>
       <c r="M38" t="n">
         <v>0.49</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.13</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45968.55208333334</v>
+        <v>45971.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3581</v>
+        <v>3811.7</v>
       </c>
       <c r="I39" t="n">
         <v>3647.577818254803</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.08</v>
+        <v>-7.59</v>
       </c>
       <c r="L39" t="n">
-        <v>4.03</v>
+        <v>8.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.62</v>
+        <v>2.21</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>6.64</v>
       </c>
       <c r="O39" t="n">
         <v>-2.52</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.51</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4410</v>
+        <v>4253.7</v>
       </c>
       <c r="I40" t="n">
         <v>4266.308378389419</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>123.1666666666667</v>
+        <v>126</v>
       </c>
       <c r="K40" t="n">
-        <v>15.7</v>
+        <v>11.6</v>
       </c>
       <c r="L40" t="n">
         <v>5.5</v>
@@ -2721,7 +3200,7 @@
         <v>3.32</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>3.43</v>
       </c>
       <c r="O40" t="n">
         <v>6.64</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.56</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46140.55208333334</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4186.1</v>
+        <v>4251.8</v>
       </c>
       <c r="I41" t="n">
         <v>4250.030759790689</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>1.59</v>
+        <v>0.04</v>
       </c>
       <c r="L41" t="n">
         <v>4.47</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>4.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4382.1</v>
+        <v>4310.7</v>
       </c>
       <c r="I42" t="n">
         <v>4314.062297272812</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>3.06</v>
+        <v>1.39</v>
       </c>
       <c r="L42" t="n">
         <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="N42" t="n">
         <v>2.98</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>4497</v>
+        <v>4624</v>
       </c>
       <c r="I43" t="n">
         <v>4564.256906759309</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.32</v>
+        <v>-7.27</v>
       </c>
       <c r="L43" t="n">
-        <v>5.2</v>
+        <v>9.33</v>
       </c>
       <c r="M43" t="n">
         <v>1.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>5.91</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>4371.3</v>
+        <v>4346.9</v>
       </c>
       <c r="I44" t="n">
         <v>4350.627704559436</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.46</v>
+        <v>-5.99</v>
       </c>
       <c r="L44" t="n">
-        <v>6.08</v>
+        <v>6.46</v>
       </c>
       <c r="M44" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="N44" t="n">
         <v>2.52</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.55</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4455</v>
+        <v>4603.8</v>
       </c>
       <c r="I45" t="n">
         <v>4574.114862554217</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.49</v>
+        <v>-5.91</v>
       </c>
       <c r="L45" t="n">
-        <v>4.9</v>
+        <v>6.09</v>
       </c>
       <c r="M45" t="n">
         <v>0.85</v>
       </c>
       <c r="N45" t="n">
-        <v>2.07</v>
+        <v>2.99</v>
       </c>
       <c r="O45" t="n">
         <v>-1.61</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.64</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46220.38541666666</v>
+        <v>46220.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>4800.8</v>
+        <v>4747</v>
       </c>
       <c r="I46" t="n">
         <v>4800.681158241924</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>4.28</v>
+        <v>3.11</v>
       </c>
       <c r="L46" t="n">
         <v>4.93</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.96</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46234.38541666666</v>
+        <v>46234.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>5099.7</v>
+        <v>5139.9</v>
       </c>
       <c r="I47" t="n">
         <v>5114.519383037243</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.43</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>8.289999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.81</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>4921.5</v>
+        <v>4846.5</v>
       </c>
       <c r="I48" t="n">
         <v>4857.188913484062</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.25</v>
+        <v>-5.71</v>
       </c>
       <c r="L48" t="n">
         <v>6.34</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3237,6 +3824,14 @@
       <c r="Q49" t="n">
         <v>72</v>
       </c>
+      <c r="R49" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5339,7 +5934,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="6">
@@ -5349,7 +5944,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="7">
@@ -5359,7 +5954,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>161.8</v>
       </c>
     </row>
     <row r="8">
@@ -5369,7 +5964,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -5379,7 +5974,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="10">
@@ -5389,7 +5984,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72.59999999999999</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="11">
@@ -5429,7 +6024,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.74</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="15">
@@ -5439,7 +6034,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.29</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="16">
@@ -5449,7 +6044,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.91</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="17">
@@ -5459,7 +6054,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.9</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="18">
@@ -5469,7 +6064,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="19">
@@ -5479,7 +6074,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.39</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="20">
@@ -5489,7 +6084,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.58</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="21">
@@ -5499,7 +6094,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.460000000000001</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="22">
@@ -5509,7 +6104,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -5519,7 +6114,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5529,7 +6124,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -5539,7 +6134,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.2</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="26">
@@ -5549,7 +6144,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.77</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="27">
@@ -5559,7 +6154,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.11</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="28">
@@ -5569,7 +6164,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
